--- a/Results/5th Sem Results AIML 2.xlsx
+++ b/Results/5th Sem Results AIML 2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Imp\Coding\Python\Projects\Selenium\RGPV Result Bot\Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{102D34FC-4B26-4C3E-9AD6-47F7FE05A12C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F88038B-7166-4B4D-89A1-38B3013B0392}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{6B8163A5-99D5-42D5-BAE9-C4DDFFD45228}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1518" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1518" uniqueCount="157">
   <si>
     <t>Roll No.</t>
   </si>
@@ -37,18 +37,6 @@
   </si>
   <si>
     <t>CGPA</t>
-  </si>
-  <si>
-    <t>AL-401</t>
-  </si>
-  <si>
-    <t>AL-402</t>
-  </si>
-  <si>
-    <t>AL-403</t>
-  </si>
-  <si>
-    <t>AL-404</t>
   </si>
   <si>
     <t>0827AL221080</t>
@@ -1099,10 +1087,10 @@
     <tableColumn id="3" xr3:uid="{0463C325-FD6C-4FE8-8918-26C8F2605C25}" name="Result"/>
     <tableColumn id="4" xr3:uid="{746E8826-D8A4-41FB-A7DD-55F8E9C3019F}" name="SGPA"/>
     <tableColumn id="5" xr3:uid="{375B7D44-12C5-4502-828D-BEA2CF7B8AFC}" name="CGPA"/>
-    <tableColumn id="6" xr3:uid="{A7BC5854-9F9D-4F9D-8DB8-825A6228A97B}" name="AL-401"/>
-    <tableColumn id="7" xr3:uid="{BE93E312-349F-4D81-96B2-1E06F5648ECE}" name="AL-402"/>
-    <tableColumn id="8" xr3:uid="{E6232ABD-46A0-44B4-B4AC-BA1BD7D72CD8}" name="AL-403"/>
-    <tableColumn id="9" xr3:uid="{48976C91-326B-4113-A0F1-3D2159916C55}" name="AL-404"/>
+    <tableColumn id="6" xr3:uid="{A7BC5854-9F9D-4F9D-8DB8-825A6228A97B}" name="AL-501"/>
+    <tableColumn id="7" xr3:uid="{BE93E312-349F-4D81-96B2-1E06F5648ECE}" name="AL-502"/>
+    <tableColumn id="8" xr3:uid="{E6232ABD-46A0-44B4-B4AC-BA1BD7D72CD8}" name="AL-503"/>
+    <tableColumn id="9" xr3:uid="{48976C91-326B-4113-A0F1-3D2159916C55}" name="AL-504"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight18" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1450,27 +1438,27 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="G1" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="H1" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="I1" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D2">
         <v>7.38</v>
@@ -1479,27 +1467,27 @@
         <v>7.28</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I2" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B3" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D3">
         <v>8.92</v>
@@ -1508,27 +1496,27 @@
         <v>8.4600000000000009</v>
       </c>
       <c r="F3" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G3" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H3" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I3" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D4">
         <v>7.63</v>
@@ -1537,27 +1525,27 @@
         <v>7.21</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H4" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I4" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D5">
         <v>7.29</v>
@@ -1566,27 +1554,27 @@
         <v>6.74</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G5" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H5" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I5" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C6" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D6">
         <v>6.38</v>
@@ -1595,27 +1583,27 @@
         <v>5.7</v>
       </c>
       <c r="F6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H6" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D7">
         <v>7.46</v>
@@ -1624,27 +1612,27 @@
         <v>6.54</v>
       </c>
       <c r="F7" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G7" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H7" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I7" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D8">
         <v>7.5</v>
@@ -1653,27 +1641,27 @@
         <v>6.46</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G8" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H8" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I8" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C9" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D9">
         <v>7</v>
@@ -1682,27 +1670,27 @@
         <v>6.59</v>
       </c>
       <c r="F9" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G9" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H9" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I9" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C10" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D10">
         <v>6.71</v>
@@ -1711,27 +1699,27 @@
         <v>5.85</v>
       </c>
       <c r="F10" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G10" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H10" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="I10" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B11" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D11">
         <v>6.71</v>
@@ -1740,27 +1728,27 @@
         <v>6.4</v>
       </c>
       <c r="F11" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G11" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H11" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I11" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D12">
         <v>6.17</v>
@@ -1769,27 +1757,27 @@
         <v>5.58</v>
       </c>
       <c r="F12" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G12" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H12" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I12" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B13" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D13">
         <v>7.29</v>
@@ -1798,27 +1786,27 @@
         <v>6.21</v>
       </c>
       <c r="F13" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G13" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H13" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I13" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B14" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D14">
         <v>7.92</v>
@@ -1827,27 +1815,27 @@
         <v>7.12</v>
       </c>
       <c r="F14" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G14" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H14" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I14" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B15" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C15" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D15">
         <v>8.2100000000000009</v>
@@ -1856,27 +1844,27 @@
         <v>7</v>
       </c>
       <c r="F15" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G15" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H15" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I15" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B16" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C16" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D16">
         <v>6.92</v>
@@ -1885,27 +1873,27 @@
         <v>6.72</v>
       </c>
       <c r="F16" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G16" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H16" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I16" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C17" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D17">
         <v>6.67</v>
@@ -1914,27 +1902,27 @@
         <v>6.28</v>
       </c>
       <c r="F17" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G17" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H17" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I17" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B18" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C18" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D18">
         <v>7.46</v>
@@ -1943,27 +1931,27 @@
         <v>7.17</v>
       </c>
       <c r="F18" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G18" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H18" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I18" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B19" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C19" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D19">
         <v>8.67</v>
@@ -1972,27 +1960,27 @@
         <v>8.02</v>
       </c>
       <c r="F19" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G19" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H19" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I19" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B20" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C20" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D20">
         <v>7</v>
@@ -2001,27 +1989,27 @@
         <v>6.97</v>
       </c>
       <c r="F20" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G20" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H20" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I20" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B21" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C21" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D21">
         <v>6.67</v>
@@ -2030,27 +2018,27 @@
         <v>6.03</v>
       </c>
       <c r="F21" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G21" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H21" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I21" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B22" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C22" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D22">
         <v>6.88</v>
@@ -2059,27 +2047,27 @@
         <v>6.54</v>
       </c>
       <c r="F22" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G22" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H22" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I22" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B23" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C23" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D23">
         <v>6.92</v>
@@ -2088,27 +2076,27 @@
         <v>6.55</v>
       </c>
       <c r="F23" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G23" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H23" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I23" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B24" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C24" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D24">
         <v>7.96</v>
@@ -2117,27 +2105,27 @@
         <v>7.05</v>
       </c>
       <c r="F24" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G24" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H24" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I24" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B25" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C25" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D25">
         <v>7.33</v>
@@ -2146,27 +2134,27 @@
         <v>6.91</v>
       </c>
       <c r="F25" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G25" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H25" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I25" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B26" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C26" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D26">
         <v>7.5</v>
@@ -2175,27 +2163,27 @@
         <v>7.47</v>
       </c>
       <c r="F26" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G26" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H26" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I26" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B27" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C27" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D27">
         <v>7.67</v>
@@ -2204,27 +2192,27 @@
         <v>6.97</v>
       </c>
       <c r="F27" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G27" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H27" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I27" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B28" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C28" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D28">
         <v>7.04</v>
@@ -2233,27 +2221,27 @@
         <v>6.78</v>
       </c>
       <c r="F28" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G28" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H28" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I28" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B29" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C29" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D29">
         <v>8.08</v>
@@ -2262,27 +2250,27 @@
         <v>7.46</v>
       </c>
       <c r="F29" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G29" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H29" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I29" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B30" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C30" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D30">
         <v>8</v>
@@ -2291,27 +2279,27 @@
         <v>7.4</v>
       </c>
       <c r="F30" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G30" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H30" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I30" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B31" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C31" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D31">
         <v>6</v>
@@ -2320,27 +2308,27 @@
         <v>5.57</v>
       </c>
       <c r="F31" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G31" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H31" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I31" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B32" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C32" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D32">
         <v>8.3800000000000008</v>
@@ -2349,27 +2337,27 @@
         <v>7.41</v>
       </c>
       <c r="F32" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G32" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H32" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I32" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B33" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C33" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D33">
         <v>6.96</v>
@@ -2378,27 +2366,27 @@
         <v>6.26</v>
       </c>
       <c r="F33" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G33" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H33" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I33" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B34" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C34" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D34">
         <v>7.63</v>
@@ -2407,27 +2395,27 @@
         <v>6.89</v>
       </c>
       <c r="F34" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G34" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H34" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I34" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B35" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C35" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D35">
         <v>6.29</v>
@@ -2436,27 +2424,27 @@
         <v>5.6</v>
       </c>
       <c r="F35" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G35" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H35" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I35" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B36" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C36" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D36">
         <v>8.25</v>
@@ -2465,27 +2453,27 @@
         <v>7.41</v>
       </c>
       <c r="F36" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G36" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H36" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I36" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B37" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C37" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D37">
         <v>6.29</v>
@@ -2494,27 +2482,27 @@
         <v>5.86</v>
       </c>
       <c r="F37" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G37" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H37" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I37" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B38" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C38" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D38">
         <v>6.67</v>
@@ -2523,27 +2511,27 @@
         <v>6.39</v>
       </c>
       <c r="F38" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G38" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H38" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I38" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B39" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C39" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D39">
         <v>7.79</v>
@@ -2552,27 +2540,27 @@
         <v>7.1</v>
       </c>
       <c r="F39" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G39" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H39" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I39" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B40" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C40" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D40">
         <v>5.88</v>
@@ -2581,27 +2569,27 @@
         <v>5.71</v>
       </c>
       <c r="F40" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G40" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H40" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="I40" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B41" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C41" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D41">
         <v>7.46</v>
@@ -2610,27 +2598,27 @@
         <v>6.69</v>
       </c>
       <c r="F41" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G41" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H41" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I41" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B42" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C42" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D42">
         <v>7.38</v>
@@ -2639,27 +2627,27 @@
         <v>6.39</v>
       </c>
       <c r="F42" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G42" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H42" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I42" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B43" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C43" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D43">
         <v>7.96</v>
@@ -2668,27 +2656,27 @@
         <v>7.34</v>
       </c>
       <c r="F43" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G43" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H43" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I43" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B44" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C44" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D44">
         <v>8.0399999999999991</v>
@@ -2697,27 +2685,27 @@
         <v>7.41</v>
       </c>
       <c r="F44" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G44" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H44" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I44" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B45" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C45" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D45">
         <v>8</v>
@@ -2726,27 +2714,27 @@
         <v>7.15</v>
       </c>
       <c r="F45" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G45" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H45" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I45" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B46" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C46" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D46">
         <v>7.79</v>
@@ -2755,27 +2743,27 @@
         <v>6.59</v>
       </c>
       <c r="F46" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G46" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H46" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I46" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B47" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C47" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D47">
         <v>7.08</v>
@@ -2784,27 +2772,27 @@
         <v>6.1</v>
       </c>
       <c r="F47" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G47" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H47" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I47" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B48" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C48" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D48">
         <v>8.17</v>
@@ -2813,27 +2801,27 @@
         <v>7.21</v>
       </c>
       <c r="F48" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G48" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H48" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I48" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B49" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C49" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D49">
         <v>8.2100000000000009</v>
@@ -2842,27 +2830,27 @@
         <v>7.18</v>
       </c>
       <c r="F49" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G49" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H49" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I49" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B50" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C50" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D50">
         <v>7.42</v>
@@ -2871,27 +2859,27 @@
         <v>6.54</v>
       </c>
       <c r="F50" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G50" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H50" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I50" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B51" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C51" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D51">
         <v>8.25</v>
@@ -2900,27 +2888,27 @@
         <v>7.87</v>
       </c>
       <c r="F51" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G51" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H51" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I51" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B52" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C52" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D52">
         <v>8.5</v>
@@ -2929,27 +2917,27 @@
         <v>7.73</v>
       </c>
       <c r="F52" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G52" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H52" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I52" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B53" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C53" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D53">
         <v>7.67</v>
@@ -2958,27 +2946,27 @@
         <v>6.47</v>
       </c>
       <c r="F53" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G53" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H53" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I53" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B54" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C54" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D54">
         <v>7.25</v>
@@ -2987,27 +2975,27 @@
         <v>6.55</v>
       </c>
       <c r="F54" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G54" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H54" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I54" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="B55" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C55" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D55">
         <v>7.46</v>
@@ -3016,27 +3004,27 @@
         <v>6.73</v>
       </c>
       <c r="F55" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G55" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H55" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I55" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B56" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C56" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D56">
         <v>5.88</v>
@@ -3045,27 +3033,27 @@
         <v>5.72</v>
       </c>
       <c r="F56" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G56" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H56" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I56" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B57" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C57" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D57">
         <v>7.5</v>
@@ -3074,27 +3062,27 @@
         <v>7.36</v>
       </c>
       <c r="F57" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G57" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H57" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I57" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B58" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C58" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D58">
         <v>6.25</v>
@@ -3103,27 +3091,27 @@
         <v>6.26</v>
       </c>
       <c r="F58" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G58" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H58" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I58" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B59" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C59" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D59">
         <v>5.92</v>
@@ -3132,27 +3120,27 @@
         <v>6.04</v>
       </c>
       <c r="F59" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G59" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H59" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I59" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B60" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C60" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D60">
         <v>7.58</v>
@@ -3161,27 +3149,27 @@
         <v>6.81</v>
       </c>
       <c r="F60" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G60" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H60" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I60" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B61" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C61" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D61">
         <v>7.33</v>
@@ -3190,27 +3178,27 @@
         <v>7.14</v>
       </c>
       <c r="F61" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G61" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H61" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I61" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B62" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C62" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D62">
         <v>7.5</v>
@@ -3219,27 +3207,27 @@
         <v>7.19</v>
       </c>
       <c r="F62" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G62" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H62" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I62" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B63" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C63" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D63">
         <v>5.29</v>
@@ -3248,27 +3236,27 @@
         <v>5.08</v>
       </c>
       <c r="F63" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G63" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H63" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I63" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B64" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C64" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D64">
         <v>5.33</v>
@@ -3277,27 +3265,27 @@
         <v>5.22</v>
       </c>
       <c r="F64" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G64" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H64" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="I64" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B65" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C65" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D65">
         <v>6.13</v>
@@ -3306,27 +3294,27 @@
         <v>6.06</v>
       </c>
       <c r="F65" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G65" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H65" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I65" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B66" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C66" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D66">
         <v>7.92</v>
@@ -3335,27 +3323,27 @@
         <v>7.13</v>
       </c>
       <c r="F66" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G66" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H66" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I66" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B67" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C67" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D67">
         <v>6.75</v>
@@ -3364,27 +3352,27 @@
         <v>5.87</v>
       </c>
       <c r="F67" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G67" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H67" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I67" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B68" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="C68" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D68">
         <v>7.13</v>
@@ -3393,27 +3381,27 @@
         <v>6.99</v>
       </c>
       <c r="F68" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G68" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H68" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I68" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="B69" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C69" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D69">
         <v>5.21</v>
@@ -3422,27 +3410,27 @@
         <v>5.45</v>
       </c>
       <c r="F69" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G69" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H69" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="I69" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B70" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C70" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D70">
         <v>8.6300000000000008</v>
@@ -3451,27 +3439,27 @@
         <v>8.25</v>
       </c>
       <c r="F70" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G70" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H70" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I70" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="B71" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C71" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D71">
         <v>8.67</v>
@@ -3480,27 +3468,27 @@
         <v>8.24</v>
       </c>
       <c r="F71" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G71" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H71" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I71" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="B72" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="C72" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D72">
         <v>7.83</v>
@@ -3509,16 +3497,16 @@
         <v>7.67</v>
       </c>
       <c r="F72" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G72" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H72" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I72" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -3556,27 +3544,27 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="G1" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="H1" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="I1" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B2" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D2">
         <v>8.92</v>
@@ -3585,27 +3573,27 @@
         <v>8.4600000000000009</v>
       </c>
       <c r="F2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B3" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D3">
         <v>8.67</v>
@@ -3614,27 +3602,27 @@
         <v>8.02</v>
       </c>
       <c r="F3" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G3" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H3" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I3" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="B4" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D4">
         <v>8.67</v>
@@ -3643,27 +3631,27 @@
         <v>8.24</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B5" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D5">
         <v>8.6300000000000008</v>
@@ -3672,27 +3660,27 @@
         <v>8.25</v>
       </c>
       <c r="F5" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G5" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H5" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I5" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C6" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D6">
         <v>8.5</v>
@@ -3701,27 +3689,27 @@
         <v>7.73</v>
       </c>
       <c r="F6" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G6" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H6" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I6" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B7" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D7">
         <v>8.3800000000000008</v>
@@ -3730,27 +3718,27 @@
         <v>7.41</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G7" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H7" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I7" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B8" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C8" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D8">
         <v>8.25</v>
@@ -3759,27 +3747,27 @@
         <v>7.41</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G8" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H8" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I8" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B9" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C9" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D9">
         <v>8.25</v>
@@ -3788,27 +3776,27 @@
         <v>7.87</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G9" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H9" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I9" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B10" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C10" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D10">
         <v>8.2100000000000009</v>
@@ -3817,27 +3805,27 @@
         <v>7</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G10" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H10" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I10" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B11" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C11" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D11">
         <v>8.2100000000000009</v>
@@ -3846,27 +3834,27 @@
         <v>7.18</v>
       </c>
       <c r="F11" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G11" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H11" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I11" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B12" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C12" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D12">
         <v>8.17</v>
@@ -3875,27 +3863,27 @@
         <v>7.21</v>
       </c>
       <c r="F12" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G12" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H12" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I12" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B13" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C13" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D13">
         <v>8.08</v>
@@ -3904,27 +3892,27 @@
         <v>7.46</v>
       </c>
       <c r="F13" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G13" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H13" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I13" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B14" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C14" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D14">
         <v>8.0399999999999991</v>
@@ -3933,27 +3921,27 @@
         <v>7.41</v>
       </c>
       <c r="F14" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G14" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H14" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I14" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B15" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C15" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D15">
         <v>8</v>
@@ -3962,27 +3950,27 @@
         <v>7.4</v>
       </c>
       <c r="F15" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G15" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H15" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I15" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B16" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C16" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D16">
         <v>8</v>
@@ -3991,27 +3979,27 @@
         <v>7.15</v>
       </c>
       <c r="F16" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G16" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H16" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I16" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B17" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C17" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D17">
         <v>7.96</v>
@@ -4020,27 +4008,27 @@
         <v>7.05</v>
       </c>
       <c r="F17" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G17" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H17" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I17" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B18" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C18" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D18">
         <v>7.96</v>
@@ -4049,27 +4037,27 @@
         <v>7.34</v>
       </c>
       <c r="F18" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G18" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H18" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I18" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B19" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C19" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D19">
         <v>7.92</v>
@@ -4078,27 +4066,27 @@
         <v>7.12</v>
       </c>
       <c r="F19" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G19" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H19" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I19" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B20" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C20" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D20">
         <v>7.92</v>
@@ -4107,27 +4095,27 @@
         <v>7.13</v>
       </c>
       <c r="F20" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G20" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H20" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I20" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="B21" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="C21" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D21">
         <v>7.83</v>
@@ -4136,27 +4124,27 @@
         <v>7.67</v>
       </c>
       <c r="F21" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G21" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H21" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I21" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B22" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C22" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D22">
         <v>7.79</v>
@@ -4165,27 +4153,27 @@
         <v>7.1</v>
       </c>
       <c r="F22" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G22" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H22" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I22" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B23" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C23" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D23">
         <v>7.79</v>
@@ -4194,27 +4182,27 @@
         <v>6.59</v>
       </c>
       <c r="F23" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G23" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H23" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I23" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B24" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C24" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D24">
         <v>7.67</v>
@@ -4223,27 +4211,27 @@
         <v>6.97</v>
       </c>
       <c r="F24" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G24" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H24" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I24" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B25" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C25" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D25">
         <v>7.67</v>
@@ -4252,27 +4240,27 @@
         <v>6.47</v>
       </c>
       <c r="F25" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G25" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H25" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I25" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B26" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C26" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D26">
         <v>7.63</v>
@@ -4281,27 +4269,27 @@
         <v>7.21</v>
       </c>
       <c r="F26" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G26" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H26" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I26" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B27" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C27" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D27">
         <v>7.63</v>
@@ -4310,27 +4298,27 @@
         <v>6.89</v>
       </c>
       <c r="F27" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G27" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H27" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I27" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B28" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C28" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D28">
         <v>7.58</v>
@@ -4339,27 +4327,27 @@
         <v>6.81</v>
       </c>
       <c r="F28" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G28" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H28" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I28" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B29" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C29" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D29">
         <v>7.5</v>
@@ -4368,27 +4356,27 @@
         <v>6.46</v>
       </c>
       <c r="F29" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G29" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H29" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I29" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B30" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C30" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D30">
         <v>7.5</v>
@@ -4397,27 +4385,27 @@
         <v>7.47</v>
       </c>
       <c r="F30" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G30" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H30" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I30" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B31" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C31" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D31">
         <v>7.5</v>
@@ -4426,27 +4414,27 @@
         <v>7.36</v>
       </c>
       <c r="F31" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G31" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H31" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I31" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B32" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C32" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D32">
         <v>7.5</v>
@@ -4455,27 +4443,27 @@
         <v>7.19</v>
       </c>
       <c r="F32" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G32" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H32" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I32" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B33" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C33" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D33">
         <v>7.46</v>
@@ -4484,27 +4472,27 @@
         <v>6.54</v>
       </c>
       <c r="F33" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G33" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H33" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I33" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B34" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C34" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D34">
         <v>7.46</v>
@@ -4513,27 +4501,27 @@
         <v>7.17</v>
       </c>
       <c r="F34" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G34" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H34" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I34" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B35" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C35" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D35">
         <v>7.46</v>
@@ -4542,27 +4530,27 @@
         <v>6.69</v>
       </c>
       <c r="F35" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G35" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H35" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I35" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="B36" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C36" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D36">
         <v>7.46</v>
@@ -4571,27 +4559,27 @@
         <v>6.73</v>
       </c>
       <c r="F36" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G36" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H36" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I36" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B37" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C37" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D37">
         <v>7.42</v>
@@ -4600,27 +4588,27 @@
         <v>6.54</v>
       </c>
       <c r="F37" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G37" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H37" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I37" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B38" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C38" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D38">
         <v>7.38</v>
@@ -4629,27 +4617,27 @@
         <v>7.28</v>
       </c>
       <c r="F38" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G38" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H38" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I38" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B39" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C39" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D39">
         <v>7.38</v>
@@ -4658,27 +4646,27 @@
         <v>6.39</v>
       </c>
       <c r="F39" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G39" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H39" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I39" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B40" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C40" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D40">
         <v>7.33</v>
@@ -4687,27 +4675,27 @@
         <v>6.91</v>
       </c>
       <c r="F40" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G40" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H40" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I40" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B41" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C41" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D41">
         <v>7.33</v>
@@ -4716,27 +4704,27 @@
         <v>7.14</v>
       </c>
       <c r="F41" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G41" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H41" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I41" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B42" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C42" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D42">
         <v>7.29</v>
@@ -4745,27 +4733,27 @@
         <v>6.74</v>
       </c>
       <c r="F42" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G42" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H42" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I42" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B43" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C43" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D43">
         <v>7.29</v>
@@ -4774,27 +4762,27 @@
         <v>6.21</v>
       </c>
       <c r="F43" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G43" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H43" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I43" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B44" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C44" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D44">
         <v>7.25</v>
@@ -4803,27 +4791,27 @@
         <v>6.55</v>
       </c>
       <c r="F44" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G44" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H44" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I44" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B45" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="C45" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D45">
         <v>7.13</v>
@@ -4832,27 +4820,27 @@
         <v>6.99</v>
       </c>
       <c r="F45" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G45" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H45" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I45" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B46" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C46" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D46">
         <v>7.08</v>
@@ -4861,27 +4849,27 @@
         <v>6.1</v>
       </c>
       <c r="F46" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G46" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H46" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I46" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B47" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C47" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D47">
         <v>7.04</v>
@@ -4890,27 +4878,27 @@
         <v>6.78</v>
       </c>
       <c r="F47" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G47" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H47" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I47" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B48" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C48" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D48">
         <v>7</v>
@@ -4919,27 +4907,27 @@
         <v>6.59</v>
       </c>
       <c r="F48" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G48" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H48" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I48" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B49" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C49" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D49">
         <v>7</v>
@@ -4948,27 +4936,27 @@
         <v>6.97</v>
       </c>
       <c r="F49" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G49" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H49" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I49" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B50" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C50" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D50">
         <v>6.96</v>
@@ -4977,27 +4965,27 @@
         <v>6.26</v>
       </c>
       <c r="F50" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G50" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H50" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I50" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B51" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C51" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D51">
         <v>6.92</v>
@@ -5006,27 +4994,27 @@
         <v>6.72</v>
       </c>
       <c r="F51" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G51" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H51" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I51" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C52" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D52">
         <v>6.92</v>
@@ -5035,27 +5023,27 @@
         <v>6.55</v>
       </c>
       <c r="F52" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G52" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H52" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I52" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B53" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C53" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D53">
         <v>6.88</v>
@@ -5064,27 +5052,27 @@
         <v>6.54</v>
       </c>
       <c r="F53" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G53" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H53" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I53" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B54" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C54" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D54">
         <v>6.75</v>
@@ -5093,27 +5081,27 @@
         <v>5.87</v>
       </c>
       <c r="F54" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G54" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H54" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I54" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B55" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C55" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D55">
         <v>6.71</v>
@@ -5122,27 +5110,27 @@
         <v>5.85</v>
       </c>
       <c r="F55" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G55" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H55" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="I55" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B56" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C56" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D56">
         <v>6.71</v>
@@ -5151,27 +5139,27 @@
         <v>6.4</v>
       </c>
       <c r="F56" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G56" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H56" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I56" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B57" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C57" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D57">
         <v>6.67</v>
@@ -5180,27 +5168,27 @@
         <v>6.28</v>
       </c>
       <c r="F57" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G57" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H57" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I57" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B58" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C58" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D58">
         <v>6.67</v>
@@ -5209,27 +5197,27 @@
         <v>6.03</v>
       </c>
       <c r="F58" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G58" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H58" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I58" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B59" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C59" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D59">
         <v>6.67</v>
@@ -5238,27 +5226,27 @@
         <v>6.39</v>
       </c>
       <c r="F59" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G59" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H59" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I59" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B60" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C60" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D60">
         <v>6.38</v>
@@ -5267,27 +5255,27 @@
         <v>5.7</v>
       </c>
       <c r="F60" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G60" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H60" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I60" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B61" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C61" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D61">
         <v>6.29</v>
@@ -5296,27 +5284,27 @@
         <v>5.6</v>
       </c>
       <c r="F61" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G61" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H61" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I61" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B62" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C62" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D62">
         <v>6.29</v>
@@ -5325,27 +5313,27 @@
         <v>5.86</v>
       </c>
       <c r="F62" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G62" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H62" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I62" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B63" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C63" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D63">
         <v>6.25</v>
@@ -5354,27 +5342,27 @@
         <v>6.26</v>
       </c>
       <c r="F63" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G63" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H63" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I63" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B64" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C64" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D64">
         <v>6.17</v>
@@ -5383,27 +5371,27 @@
         <v>5.58</v>
       </c>
       <c r="F64" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G64" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H64" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I64" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B65" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C65" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D65">
         <v>6.13</v>
@@ -5412,27 +5400,27 @@
         <v>6.06</v>
       </c>
       <c r="F65" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G65" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H65" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I65" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B66" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C66" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D66">
         <v>6</v>
@@ -5441,27 +5429,27 @@
         <v>5.57</v>
       </c>
       <c r="F66" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G66" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H66" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I66" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B67" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C67" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D67">
         <v>5.92</v>
@@ -5470,27 +5458,27 @@
         <v>6.04</v>
       </c>
       <c r="F67" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G67" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H67" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I67" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B68" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C68" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D68">
         <v>5.88</v>
@@ -5499,27 +5487,27 @@
         <v>5.71</v>
       </c>
       <c r="F68" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G68" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H68" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="I68" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B69" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C69" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D69">
         <v>5.88</v>
@@ -5528,27 +5516,27 @@
         <v>5.72</v>
       </c>
       <c r="F69" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G69" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H69" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I69" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B70" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C70" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D70">
         <v>5.33</v>
@@ -5557,27 +5545,27 @@
         <v>5.22</v>
       </c>
       <c r="F70" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G70" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H70" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="I70" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B71" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C71" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D71">
         <v>5.29</v>
@@ -5586,27 +5574,27 @@
         <v>5.08</v>
       </c>
       <c r="F71" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G71" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H71" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I71" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="B72" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C72" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D72">
         <v>5.21</v>
@@ -5615,16 +5603,16 @@
         <v>5.45</v>
       </c>
       <c r="F72" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G72" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H72" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="I72" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -5705,27 +5693,27 @@
         <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>5</v>
+        <v>153</v>
       </c>
       <c r="G1" t="s">
-        <v>6</v>
+        <v>154</v>
       </c>
       <c r="H1" t="s">
-        <v>7</v>
+        <v>155</v>
       </c>
       <c r="I1" t="s">
-        <v>8</v>
+        <v>156</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B2" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D2">
         <v>8.92</v>
@@ -5734,27 +5722,27 @@
         <v>8.4600000000000009</v>
       </c>
       <c r="F2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="B3" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D3">
         <v>8.6300000000000008</v>
@@ -5763,27 +5751,27 @@
         <v>8.25</v>
       </c>
       <c r="F3" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G3" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H3" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I3" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="B4" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D4">
         <v>8.67</v>
@@ -5792,27 +5780,27 @@
         <v>8.24</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I4" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B5" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D5">
         <v>8.67</v>
@@ -5821,27 +5809,27 @@
         <v>8.02</v>
       </c>
       <c r="F5" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G5" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H5" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I5" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B6" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C6" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D6">
         <v>8.25</v>
@@ -5850,27 +5838,27 @@
         <v>7.87</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G6" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H6" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I6" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="B7" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C7" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D7">
         <v>8.5</v>
@@ -5879,27 +5867,27 @@
         <v>7.73</v>
       </c>
       <c r="F7" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G7" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H7" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I7" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="B8" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="C8" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D8">
         <v>7.83</v>
@@ -5908,27 +5896,27 @@
         <v>7.67</v>
       </c>
       <c r="F8" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G8" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H8" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I8" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B9" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C9" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D9">
         <v>7.5</v>
@@ -5937,27 +5925,27 @@
         <v>7.47</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G9" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H9" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I9" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="B10" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C10" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D10">
         <v>8.08</v>
@@ -5966,27 +5954,27 @@
         <v>7.46</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G10" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H10" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I10" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B11" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C11" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D11">
         <v>8.3800000000000008</v>
@@ -5995,27 +5983,27 @@
         <v>7.41</v>
       </c>
       <c r="F11" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G11" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H11" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I11" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B12" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C12" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D12">
         <v>8.25</v>
@@ -6024,27 +6012,27 @@
         <v>7.41</v>
       </c>
       <c r="F12" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G12" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H12" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I12" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B13" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C13" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D13">
         <v>8.0399999999999991</v>
@@ -6053,27 +6041,27 @@
         <v>7.41</v>
       </c>
       <c r="F13" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G13" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H13" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I13" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B14" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C14" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D14">
         <v>8</v>
@@ -6082,27 +6070,27 @@
         <v>7.4</v>
       </c>
       <c r="F14" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G14" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H14" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I14" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B15" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C15" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D15">
         <v>7.5</v>
@@ -6111,27 +6099,27 @@
         <v>7.36</v>
       </c>
       <c r="F15" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G15" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H15" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I15" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B16" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C16" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D16">
         <v>7.96</v>
@@ -6140,27 +6128,27 @@
         <v>7.34</v>
       </c>
       <c r="F16" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G16" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H16" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I16" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B17" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C17" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D17">
         <v>7.38</v>
@@ -6169,27 +6157,27 @@
         <v>7.28</v>
       </c>
       <c r="F17" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G17" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H17" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I17" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B18" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C18" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D18">
         <v>7.63</v>
@@ -6198,27 +6186,27 @@
         <v>7.21</v>
       </c>
       <c r="F18" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G18" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H18" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I18" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B19" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C19" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D19">
         <v>8.17</v>
@@ -6227,27 +6215,27 @@
         <v>7.21</v>
       </c>
       <c r="F19" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G19" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H19" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I19" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="B20" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C20" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D20">
         <v>7.5</v>
@@ -6256,27 +6244,27 @@
         <v>7.19</v>
       </c>
       <c r="F20" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G20" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H20" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I20" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B21" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C21" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D21">
         <v>8.2100000000000009</v>
@@ -6285,27 +6273,27 @@
         <v>7.18</v>
       </c>
       <c r="F21" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G21" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H21" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I21" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B22" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C22" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D22">
         <v>7.46</v>
@@ -6314,27 +6302,27 @@
         <v>7.17</v>
       </c>
       <c r="F22" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G22" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H22" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I22" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B23" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C23" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D23">
         <v>8</v>
@@ -6343,27 +6331,27 @@
         <v>7.15</v>
       </c>
       <c r="F23" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G23" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H23" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I23" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="B24" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C24" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D24">
         <v>7.33</v>
@@ -6372,27 +6360,27 @@
         <v>7.14</v>
       </c>
       <c r="F24" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G24" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H24" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I24" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="B25" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="C25" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D25">
         <v>7.92</v>
@@ -6401,27 +6389,27 @@
         <v>7.13</v>
       </c>
       <c r="F25" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G25" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H25" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I25" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B26" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C26" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D26">
         <v>7.92</v>
@@ -6430,27 +6418,27 @@
         <v>7.12</v>
       </c>
       <c r="F26" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G26" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H26" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I26" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B27" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C27" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D27">
         <v>7.79</v>
@@ -6459,27 +6447,27 @@
         <v>7.1</v>
       </c>
       <c r="F27" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G27" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H27" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I27" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B28" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C28" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D28">
         <v>7.96</v>
@@ -6488,27 +6476,27 @@
         <v>7.05</v>
       </c>
       <c r="F28" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G28" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H28" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I28" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B29" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C29" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D29">
         <v>8.2100000000000009</v>
@@ -6517,27 +6505,27 @@
         <v>7</v>
       </c>
       <c r="F29" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G29" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H29" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I29" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B30" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="C30" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D30">
         <v>7.13</v>
@@ -6546,27 +6534,27 @@
         <v>6.99</v>
       </c>
       <c r="F30" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G30" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H30" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I30" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B31" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C31" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D31">
         <v>7</v>
@@ -6575,27 +6563,27 @@
         <v>6.97</v>
       </c>
       <c r="F31" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G31" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H31" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I31" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B32" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C32" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D32">
         <v>7.67</v>
@@ -6604,27 +6592,27 @@
         <v>6.97</v>
       </c>
       <c r="F32" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G32" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H32" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I32" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B33" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C33" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D33">
         <v>7.33</v>
@@ -6633,27 +6621,27 @@
         <v>6.91</v>
       </c>
       <c r="F33" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G33" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H33" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I33" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B34" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C34" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D34">
         <v>7.63</v>
@@ -6662,27 +6650,27 @@
         <v>6.89</v>
       </c>
       <c r="F34" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G34" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H34" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I34" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B35" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C35" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D35">
         <v>7.58</v>
@@ -6691,27 +6679,27 @@
         <v>6.81</v>
       </c>
       <c r="F35" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G35" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H35" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I35" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B36" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C36" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D36">
         <v>7.04</v>
@@ -6720,27 +6708,27 @@
         <v>6.78</v>
       </c>
       <c r="F36" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G36" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H36" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I36" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B37" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C37" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D37">
         <v>7.29</v>
@@ -6749,27 +6737,27 @@
         <v>6.74</v>
       </c>
       <c r="F37" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G37" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H37" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I37" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="B38" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C38" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D38">
         <v>7.46</v>
@@ -6778,27 +6766,27 @@
         <v>6.73</v>
       </c>
       <c r="F38" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G38" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H38" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I38" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C39" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D39">
         <v>6.92</v>
@@ -6807,27 +6795,27 @@
         <v>6.72</v>
       </c>
       <c r="F39" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G39" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H39" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I39" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B40" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C40" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D40">
         <v>7.46</v>
@@ -6836,27 +6824,27 @@
         <v>6.69</v>
       </c>
       <c r="F40" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G40" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H40" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I40" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B41" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C41" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D41">
         <v>7</v>
@@ -6865,27 +6853,27 @@
         <v>6.59</v>
       </c>
       <c r="F41" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G41" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H41" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I41" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B42" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C42" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D42">
         <v>7.79</v>
@@ -6894,27 +6882,27 @@
         <v>6.59</v>
       </c>
       <c r="F42" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G42" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H42" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I42" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B43" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C43" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D43">
         <v>6.92</v>
@@ -6923,27 +6911,27 @@
         <v>6.55</v>
       </c>
       <c r="F43" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G43" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H43" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I43" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B44" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C44" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D44">
         <v>7.25</v>
@@ -6952,27 +6940,27 @@
         <v>6.55</v>
       </c>
       <c r="F44" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G44" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H44" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I44" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B45" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C45" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D45">
         <v>7.46</v>
@@ -6981,27 +6969,27 @@
         <v>6.54</v>
       </c>
       <c r="F45" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G45" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H45" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I45" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B46" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C46" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D46">
         <v>6.88</v>
@@ -7010,27 +6998,27 @@
         <v>6.54</v>
       </c>
       <c r="F46" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G46" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H46" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I46" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B47" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C47" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D47">
         <v>7.42</v>
@@ -7039,27 +7027,27 @@
         <v>6.54</v>
       </c>
       <c r="F47" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G47" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="H47" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I47" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B48" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C48" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D48">
         <v>7.67</v>
@@ -7068,27 +7056,27 @@
         <v>6.47</v>
       </c>
       <c r="F48" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G48" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H48" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I48" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B49" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C49" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D49">
         <v>7.5</v>
@@ -7097,27 +7085,27 @@
         <v>6.46</v>
       </c>
       <c r="F49" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G49" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H49" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I49" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B50" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C50" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D50">
         <v>6.71</v>
@@ -7126,27 +7114,27 @@
         <v>6.4</v>
       </c>
       <c r="F50" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G50" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H50" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I50" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B51" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="C51" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D51">
         <v>6.67</v>
@@ -7155,27 +7143,27 @@
         <v>6.39</v>
       </c>
       <c r="F51" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G51" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H51" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I51" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B52" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C52" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D52">
         <v>7.38</v>
@@ -7184,27 +7172,27 @@
         <v>6.39</v>
       </c>
       <c r="F52" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G52" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H52" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I52" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B53" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C53" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D53">
         <v>6.67</v>
@@ -7213,27 +7201,27 @@
         <v>6.28</v>
       </c>
       <c r="F53" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G53" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H53" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I53" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="B54" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C54" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D54">
         <v>6.96</v>
@@ -7242,27 +7230,27 @@
         <v>6.26</v>
       </c>
       <c r="F54" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G54" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H54" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I54" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B55" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C55" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D55">
         <v>6.25</v>
@@ -7271,27 +7259,27 @@
         <v>6.26</v>
       </c>
       <c r="F55" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G55" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H55" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I55" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B56" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C56" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D56">
         <v>7.29</v>
@@ -7300,27 +7288,27 @@
         <v>6.21</v>
       </c>
       <c r="F56" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G56" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H56" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I56" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B57" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C57" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D57">
         <v>7.08</v>
@@ -7329,27 +7317,27 @@
         <v>6.1</v>
       </c>
       <c r="F57" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G57" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H57" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I57" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="B58" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="C58" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D58">
         <v>6.13</v>
@@ -7358,27 +7346,27 @@
         <v>6.06</v>
       </c>
       <c r="F58" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G58" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H58" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I58" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B59" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C59" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D59">
         <v>5.92</v>
@@ -7387,27 +7375,27 @@
         <v>6.04</v>
       </c>
       <c r="F59" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G59" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H59" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I59" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B60" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C60" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D60">
         <v>6.67</v>
@@ -7416,27 +7404,27 @@
         <v>6.03</v>
       </c>
       <c r="F60" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G60" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H60" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I60" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="B61" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C61" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D61">
         <v>6.75</v>
@@ -7445,27 +7433,27 @@
         <v>5.87</v>
       </c>
       <c r="F61" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G61" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H61" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I61" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="B62" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="C62" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D62">
         <v>6.29</v>
@@ -7474,27 +7462,27 @@
         <v>5.86</v>
       </c>
       <c r="F62" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G62" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H62" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I62" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="B63" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C63" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D63">
         <v>6.71</v>
@@ -7503,27 +7491,27 @@
         <v>5.85</v>
       </c>
       <c r="F63" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G63" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H63" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="I63" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="B64" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C64" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D64">
         <v>5.88</v>
@@ -7532,27 +7520,27 @@
         <v>5.72</v>
       </c>
       <c r="F64" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G64" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H64" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I64" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B65" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C65" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D65">
         <v>5.88</v>
@@ -7561,27 +7549,27 @@
         <v>5.71</v>
       </c>
       <c r="F65" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G65" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H65" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="I65" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B66" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C66" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D66">
         <v>6.38</v>
@@ -7590,27 +7578,27 @@
         <v>5.7</v>
       </c>
       <c r="F66" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="G66" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H66" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I66" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B67" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C67" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D67">
         <v>6.29</v>
@@ -7619,27 +7607,27 @@
         <v>5.6</v>
       </c>
       <c r="F67" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G67" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="H67" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I67" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B68" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C68" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D68">
         <v>6.17</v>
@@ -7648,27 +7636,27 @@
         <v>5.58</v>
       </c>
       <c r="F68" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G68" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H68" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I68" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C69" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D69">
         <v>6</v>
@@ -7677,27 +7665,27 @@
         <v>5.57</v>
       </c>
       <c r="F69" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G69" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H69" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I69" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="B70" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="C70" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D70">
         <v>5.21</v>
@@ -7706,27 +7694,27 @@
         <v>5.45</v>
       </c>
       <c r="F70" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G70" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H70" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="I70" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="B71" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C71" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D71">
         <v>5.33</v>
@@ -7735,27 +7723,27 @@
         <v>5.22</v>
       </c>
       <c r="F71" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G71" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H71" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="I71" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="B72" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="C72" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D72">
         <v>5.29</v>
@@ -7764,16 +7752,16 @@
         <v>5.08</v>
       </c>
       <c r="F72" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G72" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="H72" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I72" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
